--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2023_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:58</t>
+    <t xml:space="preserve">2026-09-24 01:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -579,10 +579,10 @@
         <v>-0.61</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="3">
@@ -602,10 +602,10 @@
         <v>-0.41</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="4">
@@ -625,7 +625,7 @@
         <v>-0.76</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>-0.57</v>
@@ -648,10 +648,10 @@
         <v>0.47</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.07</v>
+        <v>0.05</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="6">
@@ -671,10 +671,10 @@
         <v>-0.11</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="7">
@@ -947,10 +947,10 @@
         <v>-0.33</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="19">
@@ -1013,13 +1013,13 @@
         <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.54</v>
+        <v>-0.67</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.16</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="22">
@@ -1036,10 +1036,10 @@
         <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.47</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.36</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.11</v>
@@ -1059,13 +1059,13 @@
         <v>33</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="24">
@@ -1085,10 +1085,10 @@
         <v>-0.19</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="25">
@@ -1108,10 +1108,10 @@
         <v>-0.51</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1154,10 +1154,10 @@
         <v>0.62</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="28">
@@ -1180,7 +1180,7 @@
         <v>0.45</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="29">
@@ -1453,7 +1453,7 @@
         <v>-0.67</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>-0.01</v>
@@ -1519,13 +1519,13 @@
         <v>33</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.21</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="44">
@@ -1542,13 +1542,13 @@
         <v>33</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>-0.22</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="45">
@@ -1565,13 +1565,13 @@
         <v>33</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>0.14</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="46">
@@ -2025,10 +2025,10 @@
         <v>33</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>0.32</v>
@@ -2048,13 +2048,13 @@
         <v>33</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.05</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>0.35</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="67">
@@ -2071,13 +2071,13 @@
         <v>33</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2023_tarapaca.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:47</t>
+    <t xml:space="preserve">2026-10-01 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2023_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:22</t>
+    <t xml:space="preserve">2026-10-05 20:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
